--- a/docs/정책자금_추천_시스템/정책자금_간이추천시스템.xlsx
+++ b/docs/정책자금_추천_시스템/정책자금_간이추천시스템.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추천시스템" sheetId="1" r:id="R82d02904057748ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="규칙" sheetId="2" r:id="R605a8c4376034f48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="옵션" sheetId="3" r:id="R4dd85272b70b4aa6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자금설명" sheetId="4" r:id="Rc66568890e6a46a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추천시스템" sheetId="1" r:id="Rbbaab78b3d5b41e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="규칙" sheetId="2" r:id="R904cbba196724f19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="옵션" sheetId="3" r:id="Rd9ff92684c574175"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자금설명" sheetId="4" r:id="R6d9b72eae473480e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -869,14 +869,14 @@
         <x:v>상생성장지원자금</x:v>
       </x:c>
       <x:c r="B5" s="4" t="str">
-        <x:f>IF($F$11&lt;&gt;"","입력필요",IF($F$2&lt;&gt;"","불가",IF('추천시스템'!B27="예","추천",IF('추천시스템'!B9="예","검토","해당없음"))))</x:f>
+        <x:f>IF($F$11&lt;&gt;"","입력필요",IF($F$2&lt;&gt;"","불가",IF(OR('추천시스템'!B27="예",'추천시스템'!B9="예"),"추천","해당없음")))</x:f>
         <x:v>입력필요</x:v>
       </x:c>
       <x:c r="C5" s="4" t="str">
-        <x:f>IF(B5="추천","플랫폼 입점 또는 TOPS/POST-TOPS 성격이 있어 상생성장지원자금과 가장 가깝습니다.",IF(B5="검토","온라인 판매 중이라 상생성장지원자금 가능성을 추가 검토할 수 있습니다.",""))</x:f>
+        <x:f>IF(B5="추천",IF('추천시스템'!B27="예","플랫폼 입점 또는 TOPS/POST-TOPS 성격이 확인되어 상생성장지원자금과 가깝습니다.","온라인 판매가 확인되어 상생성장지원자금 추천 대상입니다."),"")</x:f>
       </x:c>
       <x:c r="D5" s="4" t="str">
-        <x:f>IF(OR(B5="추천",B5="검토"),"온라인 플랫폼 입점 증빙, TOPS/POST-TOPS 또는 추천 확인자료","")</x:f>
+        <x:f>IF(B5="추천",IF('추천시스템'!B27="예","온라인 플랫폼 입점 증빙, TOPS/POST-TOPS 또는 추천 확인자료","TOPS/POST-TOPS 참여 필요"),"")</x:f>
       </x:c>
       <x:c r="E5" s="1"/>
       <x:c r="F5" s="1" t="str">
@@ -1307,13 +1307,13 @@
         <x:v>상생성장지원자금</x:v>
       </x:c>
       <x:c r="B5" s="4" t="str">
-        <x:v>온라인 플랫폼/성장형 여부</x:v>
+        <x:v>온라인 판매 또는 플랫폼/TOPS 참여 여부</x:v>
       </x:c>
       <x:c r="C5" s="4" t="str">
         <x:v>온라인 판매, 플랫폼 입점/TOPS/POST-TOPS</x:v>
       </x:c>
       <x:c r="D5" s="4" t="str">
-        <x:v>단순 온라인 판매는 참고용 검토</x:v>
+        <x:v>온라인 판매만으로도 우선 추천하되 TOPS/POST-TOPS 참여 필요</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
